--- a/data/trans_bre/P1427-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1427-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -634,7 +634,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 0,0</t>
+          <t>-1,1; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,47</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-0,53</t>
+          <t>-0,51</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,81</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 0,0</t>
+          <t>-2,52; 0,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,41</t>
+          <t>0,38</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,66</t>
+          <t>-0,94; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,8</t>
+          <t>0,0; 0,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,11</t>
+          <t>0,12; 1,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>0,08</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>102,39%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,88</t>
+          <t>-1,17; 0,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,46</t>
+          <t>0,15; 1,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,7</t>
+          <t>-0,95; 1,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-31,91; 896,79</t>
+          <t>-58,53; 232,6</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,01</t>
+          <t>0,31</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>10,92%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 2,9</t>
+          <t>-1,35; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 3,49</t>
+          <t>0,28; 3,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,57</t>
+          <t>-1,29; 1,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-42,98; 228,17</t>
+          <t>-48,3; 229,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 1548,3</t>
+          <t>-13,51; 1688,52</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 73,78</t>
+          <t>-37,68; 94,39</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-1,68</t>
+          <t>2,21</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-20,66%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 3,8</t>
+          <t>-3,97; 4,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,15</t>
+          <t>-1,5; 5,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 2,55</t>
+          <t>-0,65; 5,2</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 76,65</t>
+          <t>-42,87; 92,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-21,56; 207,37</t>
+          <t>-30,07; 204,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,91; 33,54</t>
+          <t>-8,27; 86,04</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 6,34</t>
+          <t>-4,86; 6,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 7,11</t>
+          <t>-2,08; 7,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 6,58</t>
+          <t>-1,68; 6,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-32,55; 80,26</t>
+          <t>-32,0; 76,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-21,92; 128,51</t>
+          <t>-22,23; 131,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 45,49</t>
+          <t>-9,08; 48,04</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>1,33</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,51%</t>
+          <t>42,69%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,1; 1,51</t>
+          <t>-0,1; 1,43</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,64; 1,86</t>
+          <t>0,61; 1,84</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,22; 2,21</t>
+          <t>0,62; 2,03</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-5,39; 89,81</t>
+          <t>-4,5; 87,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,08; 232,04</t>
+          <t>45,71; 224,19</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,57; 85,86</t>
+          <t>17,26; 73,34</t>
         </is>
       </c>
     </row>
